--- a/technology_surveys/015_smart_utility_dashboard_usability_survey--technology_surveys.xlsx
+++ b/technology_surveys/015_smart_utility_dashboard_usability_survey--technology_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>feature_feedback</t>
+          <t>feature_feedback_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FeatureFeedback</t>
+          <t>Feature Feedback 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UsabilityRatings</t>
+          <t>Usabilities Ratings</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>improvement_ideas</t>
+          <t>improvement_ideas_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ImprovementIdeas</t>
+          <t>Improvement Ideas 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1262,7 +1262,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>improvement_ideas_choices</t>
+          <t>improvement_ideas_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1279,7 +1279,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>improvement_ideas_choices</t>
+          <t>improvement_ideas_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
